--- a/data/trans_orig/imc_inf-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as (tasa de respuesta: 87,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +716,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,68; 18,99</t>
+          <t>17,68; 19,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 18,92</t>
+          <t>17,24; 18,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,31; 22,2</t>
+          <t>18,23; 22,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,96; 19,13</t>
+          <t>16,94; 19,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,4; 20,21</t>
+          <t>18,62; 20,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 21,7</t>
+          <t>18,15; 21,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,97; 21,82</t>
+          <t>18,96; 21,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 18,72</t>
+          <t>17,16; 18,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,29; 19,36</t>
+          <t>18,29; 19,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 20,24</t>
+          <t>18,01; 20,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 21,42</t>
+          <t>19,05; 21,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,3; 18,65</t>
+          <t>17,27; 18,6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,29; 21,65</t>
+          <t>19,44; 21,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,34; 20,15</t>
+          <t>18,31; 20,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,55; 20,28</t>
+          <t>18,48; 20,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 22,16</t>
+          <t>18,45; 21,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,18; 23,06</t>
+          <t>20,13; 22,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,54; 20,23</t>
+          <t>18,52; 20,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 21,57</t>
+          <t>18,97; 21,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,74; 20,52</t>
+          <t>18,63; 20,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,06; 21,9</t>
+          <t>20,02; 21,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,64; 19,93</t>
+          <t>18,66; 20,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 20,51</t>
+          <t>18,98; 20,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,9; 20,96</t>
+          <t>18,87; 20,94</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,45</t>
+          <t>18,05; 19,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,35; 20,1</t>
+          <t>18,34; 20,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,76; 19,12</t>
+          <t>17,66; 18,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 19,83</t>
+          <t>17,82; 19,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,11; 19,48</t>
+          <t>18,22; 19,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,73; 20,69</t>
+          <t>18,72; 20,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,96; 19,74</t>
+          <t>18,09; 19,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,17; 21,03</t>
+          <t>19,12; 20,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,29; 19,25</t>
+          <t>18,29; 19,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,76; 20,04</t>
+          <t>18,73; 20,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 19,2</t>
+          <t>18,08; 19,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 20,2</t>
+          <t>18,78; 20,16</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,32; 19,58</t>
+          <t>18,34; 19,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 18,74</t>
+          <t>17,21; 18,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 21,09</t>
+          <t>18,75; 21,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,73; 19,94</t>
+          <t>17,78; 19,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,7; 19,06</t>
+          <t>17,73; 19,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,67; 20,95</t>
+          <t>18,6; 21,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 21,88</t>
+          <t>18,61; 21,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,52; 20,08</t>
+          <t>17,48; 20,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,18; 19,09</t>
+          <t>18,21; 19,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 19,5</t>
+          <t>18,13; 19,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,93; 20,92</t>
+          <t>18,89; 20,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,95; 19,53</t>
+          <t>17,91; 19,63</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,27; 20,48</t>
+          <t>18,18; 20,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,19; 19,72</t>
+          <t>17,22; 19,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,51; 19,27</t>
+          <t>17,45; 19,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,35; 21,31</t>
+          <t>18,47; 21,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,18; 26,34</t>
+          <t>20,04; 25,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,17; 21,31</t>
+          <t>18,21; 21,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,09; 19,95</t>
+          <t>18,1; 19,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,94; 20,85</t>
+          <t>18,94; 20,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,57; 22,6</t>
+          <t>19,43; 22,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,04; 20,21</t>
+          <t>18,03; 20,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,96; 19,24</t>
+          <t>18,0; 19,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,98; 20,65</t>
+          <t>19,02; 20,77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1416,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,61; 19,02</t>
+          <t>17,62; 19,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,78; 21,4</t>
+          <t>18,76; 21,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,55; 19,2</t>
+          <t>17,51; 19,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,83; 19,84</t>
+          <t>17,79; 19,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,82; 20,25</t>
+          <t>18,79; 20,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,62; 22,82</t>
+          <t>18,56; 22,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 20,67</t>
+          <t>18,42; 20,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,84; 28,69</t>
+          <t>18,98; 27,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,42; 19,45</t>
+          <t>18,43; 19,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,97; 21,36</t>
+          <t>18,97; 21,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,26; 19,61</t>
+          <t>18,25; 19,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,78; 23,86</t>
+          <t>18,8; 23,7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,68; 18,71</t>
+          <t>17,59; 18,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,65; 19,92</t>
+          <t>18,65; 19,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,75; 19,01</t>
+          <t>17,73; 19,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,49; 20,63</t>
+          <t>18,4; 20,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,4; 20,31</t>
+          <t>18,43; 20,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,75; 20,01</t>
+          <t>18,72; 19,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,47; 18,93</t>
+          <t>17,49; 18,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,34; 20,28</t>
+          <t>18,47; 20,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,17; 19,28</t>
+          <t>18,19; 19,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,87; 19,73</t>
+          <t>18,88; 19,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,75; 18,66</t>
+          <t>17,77; 18,69</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,62; 20,02</t>
+          <t>18,65; 19,98</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,04; 20,31</t>
+          <t>19,04; 20,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,69; 21,23</t>
+          <t>19,7; 21,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,36; 19,72</t>
+          <t>18,37; 19,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,91; 18,78</t>
+          <t>17,83; 18,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,75; 21,61</t>
+          <t>19,76; 21,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,46; 23,81</t>
+          <t>20,49; 23,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,31; 19,4</t>
+          <t>18,35; 19,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,54; 19,58</t>
+          <t>18,51; 19,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,54; 20,7</t>
+          <t>19,55; 20,68</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,42; 22,06</t>
+          <t>20,42; 22,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,49; 19,38</t>
+          <t>18,52; 19,41</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,37; 19,07</t>
+          <t>18,37; 19,05</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,75; 19,3</t>
+          <t>18,76; 19,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,99; 19,62</t>
+          <t>18,99; 19,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,55; 19,16</t>
+          <t>18,54; 19,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18,53; 19,62</t>
+          <t>18,57; 19,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,45; 20,22</t>
+          <t>19,4; 20,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,56; 20,52</t>
+          <t>19,52; 20,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,8; 19,51</t>
+          <t>18,79; 19,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,95; 19,79</t>
+          <t>18,9; 19,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,68</t>
+          <t>19,19; 19,68</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,37; 19,93</t>
+          <t>19,35; 19,92</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,73; 19,2</t>
+          <t>18,74; 19,2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,84; 19,54</t>
+          <t>18,86; 19,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Provincia-trans_orig.xlsx
@@ -716,42 +716,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,68; 19,04</t>
+          <t>17,68; 18,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,24; 18,95</t>
+          <t>17,28; 18,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,23; 22,55</t>
+          <t>18,29; 21,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 19,14</t>
+          <t>16,98; 19,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,62; 20,22</t>
+          <t>18,57; 20,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 21,85</t>
+          <t>18,35; 22,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 21,71</t>
+          <t>18,94; 21,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 18,73</t>
+          <t>17,14; 18,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 20,22</t>
+          <t>18,06; 20,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,05; 21,33</t>
+          <t>18,92; 21,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 18,6</t>
+          <t>17,26; 18,62</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,44; 21,55</t>
+          <t>19,38; 21,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,31; 20,17</t>
+          <t>18,31; 20,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 20,23</t>
+          <t>18,49; 20,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 21,9</t>
+          <t>18,48; 21,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,13; 22,85</t>
+          <t>20,18; 23,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,52; 20,23</t>
+          <t>18,57; 20,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 21,48</t>
+          <t>19,07; 21,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,63; 20,42</t>
+          <t>18,68; 20,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,02; 21,86</t>
+          <t>20,08; 21,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,66; 20,01</t>
+          <t>18,68; 19,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,98; 20,43</t>
+          <t>18,99; 20,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,87; 20,94</t>
+          <t>18,85; 20,92</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,05; 19,47</t>
+          <t>18,03; 19,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,34; 20,06</t>
+          <t>18,28; 19,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,99</t>
+          <t>17,71; 19,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,82; 19,89</t>
+          <t>17,89; 19,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,22; 19,54</t>
+          <t>18,08; 19,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,72; 20,57</t>
+          <t>18,73; 20,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,09; 19,81</t>
+          <t>18,02; 19,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,12; 20,96</t>
+          <t>19,23; 21,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,29; 19,24</t>
+          <t>18,32; 19,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,73; 20,04</t>
+          <t>18,75; 20,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 19,22</t>
+          <t>18,08; 19,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,78; 20,16</t>
+          <t>18,8; 20,15</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,34; 19,6</t>
+          <t>18,35; 19,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 18,81</t>
+          <t>17,14; 18,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 21,1</t>
+          <t>18,62; 20,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,78; 19,92</t>
+          <t>17,84; 20,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,73; 19,14</t>
+          <t>17,71; 18,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,6; 21,01</t>
+          <t>18,67; 21,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,61; 21,95</t>
+          <t>18,63; 21,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,48; 20,01</t>
+          <t>17,42; 19,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,21; 19,12</t>
+          <t>18,21; 19,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,13; 19,63</t>
+          <t>18,11; 19,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 20,79</t>
+          <t>18,97; 20,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 19,63</t>
+          <t>17,92; 19,44</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,18; 20,4</t>
+          <t>18,19; 20,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,22; 19,8</t>
+          <t>17,08; 19,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,45; 19,2</t>
+          <t>17,4; 19,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 21,53</t>
+          <t>18,45; 21,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,04; 25,93</t>
+          <t>20,15; 25,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,21; 21,66</t>
+          <t>18,17; 22,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,1; 19,99</t>
+          <t>18,13; 20,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,94; 20,8</t>
+          <t>19,02; 20,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,43; 22,21</t>
+          <t>19,53; 22,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 20,17</t>
+          <t>18,04; 20,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,0; 19,31</t>
+          <t>18,01; 19,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,02; 20,77</t>
+          <t>18,97; 20,64</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,62; 19,04</t>
+          <t>17,67; 19,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,76; 21,61</t>
+          <t>18,78; 21,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,51; 19,13</t>
+          <t>17,48; 19,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,79; 19,84</t>
+          <t>17,82; 19,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,28</t>
+          <t>18,79; 20,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,56; 22,53</t>
+          <t>18,65; 23,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,42; 20,77</t>
+          <t>18,4; 20,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,98; 27,5</t>
+          <t>18,95; 28,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,43; 19,5</t>
+          <t>18,43; 19,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,97; 21,54</t>
+          <t>18,87; 21,19</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,25; 19,69</t>
+          <t>18,28; 19,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,8; 23,7</t>
+          <t>18,73; 24,07</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,59; 18,67</t>
+          <t>17,71; 18,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,65; 19,87</t>
+          <t>18,66; 19,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,73; 19,01</t>
+          <t>17,72; 19,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,4; 20,52</t>
+          <t>18,43; 20,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,43; 20,63</t>
+          <t>18,35; 20,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,72; 19,92</t>
+          <t>18,69; 19,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,49; 18,91</t>
+          <t>17,51; 18,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,47; 20,29</t>
+          <t>18,48; 20,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,19; 19,26</t>
+          <t>18,22; 19,28</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,88; 19,78</t>
+          <t>18,84; 19,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,77; 18,69</t>
+          <t>17,77; 18,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,65; 19,98</t>
+          <t>18,66; 20,05</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,04; 20,39</t>
+          <t>19,04; 20,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,7; 21,35</t>
+          <t>19,76; 21,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,37; 19,75</t>
+          <t>18,38; 19,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,83; 18,7</t>
+          <t>17,89; 18,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,76; 21,46</t>
+          <t>19,71; 21,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,49; 23,72</t>
+          <t>20,5; 23,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,35; 19,53</t>
+          <t>18,36; 19,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,51; 19,56</t>
+          <t>18,51; 19,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,55; 20,68</t>
+          <t>19,56; 20,64</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,42; 22,07</t>
+          <t>20,42; 22,26</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,41</t>
+          <t>18,52; 19,37</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,37; 19,05</t>
+          <t>18,35; 19,04</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,76; 19,34</t>
+          <t>18,72; 19,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,99; 19,63</t>
+          <t>18,97; 19,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,54; 19,17</t>
+          <t>18,53; 19,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18,57; 19,73</t>
+          <t>18,56; 19,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,4; 20,19</t>
+          <t>19,46; 20,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,52; 20,45</t>
+          <t>19,55; 20,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,79; 19,51</t>
+          <t>18,75; 19,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,9; 19,75</t>
+          <t>18,94; 19,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,19; 19,68</t>
+          <t>19,18; 19,66</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,35; 19,92</t>
+          <t>19,35; 19,94</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,74; 19,2</t>
+          <t>18,73; 19,21</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,86; 19,51</t>
+          <t>18,87; 19,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19,35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19,54</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20,3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17,98</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>18,29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18,08</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19,66</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18,02</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,35</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,54</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,3</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,85</t>
+          <t>18,19</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,93</t>
+          <t>18,08</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,68; 18,93</t>
+          <t>18,4; 20,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,28; 18,96</t>
+          <t>18,32; 21,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,29; 21,94</t>
+          <t>18,97; 21,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,98; 19,29</t>
+          <t>17,23; 18,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,57; 20,29</t>
+          <t>17,68; 18,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,35; 22,04</t>
+          <t>17,27; 18,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,94; 21,74</t>
+          <t>18,31; 22,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,14; 18,75</t>
+          <t>17,45; 19,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,29; 19,41</t>
+          <t>18,29; 19,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,06; 20,11</t>
+          <t>18,11; 20,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,92; 21,33</t>
+          <t>18,96; 21,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,26; 18,62</t>
+          <t>17,52; 18,74</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19,28</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,97</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19,57</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>20,31</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19,16</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>19,25</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,89</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,26</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,28</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,97</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,51</t>
+          <t>19,11</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,71</t>
+          <t>19,35</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,38; 21,61</t>
+          <t>20,18; 23,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,31; 20,13</t>
+          <t>18,54; 20,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,49; 20,15</t>
+          <t>18,97; 21,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 21,8</t>
+          <t>18,8; 20,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,18; 23,12</t>
+          <t>19,29; 21,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,57; 20,3</t>
+          <t>18,34; 20,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,07; 21,74</t>
+          <t>18,55; 20,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,68; 20,48</t>
+          <t>18,17; 20,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,08; 21,88</t>
+          <t>20,06; 21,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,91</t>
+          <t>18,64; 19,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,99; 20,52</t>
+          <t>18,97; 20,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,85; 20,92</t>
+          <t>18,69; 20,25</t>
         </is>
       </c>
     </row>
@@ -928,44 +928,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18,81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,51</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,8</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20,16</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>18,69</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19,11</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18,38</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>18,69</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,81</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,51</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,8</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>20,09</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18,76</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,43</t>
+          <t>19,44</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,37</t>
+          <t>18,11; 19,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 19,99</t>
+          <t>18,73; 20,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,71; 19,06</t>
+          <t>17,96; 19,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,89; 19,92</t>
+          <t>19,27; 21,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 19,44</t>
+          <t>18,03; 19,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,73; 20,74</t>
+          <t>18,35; 20,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,02; 19,74</t>
+          <t>17,76; 19,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,23; 21,11</t>
+          <t>17,96; 19,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,32; 19,24</t>
+          <t>18,29; 19,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,75; 20,05</t>
+          <t>18,76; 20,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 19,24</t>
+          <t>18,1; 19,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 20,15</t>
+          <t>18,81; 20,21</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18,32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,53</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,89</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,53</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>18,95</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17,88</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19,64</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,75</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,32</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,53</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,89</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,59</t>
+          <t>18,79</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,66</t>
+          <t>18,65</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,35; 19,62</t>
+          <t>17,7; 19,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,14; 18,67</t>
+          <t>18,67; 20,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 20,93</t>
+          <t>18,66; 21,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,84; 20,08</t>
+          <t>17,49; 20,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,71; 18,97</t>
+          <t>18,32; 19,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,67; 21,05</t>
+          <t>17,21; 18,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,63; 21,68</t>
+          <t>18,66; 21,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,42; 19,92</t>
+          <t>17,8; 20,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,21; 19,11</t>
+          <t>18,18; 19,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 19,5</t>
+          <t>18,12; 19,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,97; 20,91</t>
+          <t>18,93; 20,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,92; 19,44</t>
+          <t>17,91; 19,5</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19,52</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18,91</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19,95</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>19,23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>18,34</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,22</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,64</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,62</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,52</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,91</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,86</t>
+          <t>19,54</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,76</t>
+          <t>19,75</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,19; 20,45</t>
+          <t>20,18; 26,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,08; 19,75</t>
+          <t>18,17; 21,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,4; 19,24</t>
+          <t>18,09; 19,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,45; 21,49</t>
+          <t>19,07; 20,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,15; 25,38</t>
+          <t>18,27; 20,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,17; 22,04</t>
+          <t>17,19; 19,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,13; 20,01</t>
+          <t>17,51; 19,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,02; 20,94</t>
+          <t>18,25; 21,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,53; 22,41</t>
+          <t>19,57; 22,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,04; 20,18</t>
+          <t>18,04; 20,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,34</t>
+          <t>17,96; 19,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,97; 20,64</t>
+          <t>18,99; 20,65</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,51</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19,83</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19,51</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21,56</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>18,28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>19,72</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>18,38</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18,62</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,51</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,83</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19,51</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21,42</t>
+          <t>18,74</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,15</t>
+          <t>20,18</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,67; 19,08</t>
+          <t>18,82; 20,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,78; 21,56</t>
+          <t>18,62; 22,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,48; 19,15</t>
+          <t>18,47; 20,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,82; 19,92</t>
+          <t>18,88; 28,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,29</t>
+          <t>17,61; 19,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,65; 23,29</t>
+          <t>18,78; 21,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,4; 20,76</t>
+          <t>17,55; 19,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,95; 28,61</t>
+          <t>17,92; 20,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,43; 19,49</t>
+          <t>18,42; 19,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,87; 21,19</t>
+          <t>18,97; 21,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,28; 19,67</t>
+          <t>18,26; 19,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,73; 24,07</t>
+          <t>18,83; 23,69</t>
         </is>
       </c>
     </row>
@@ -1488,54 +1488,54 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19,07</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19,32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18,02</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19,35</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>18,17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>19,25</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>18,33</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>19,13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>18,62</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>19,28</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,07</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,32</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,02</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>19,15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>18,62</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19,28</t>
-        </is>
-      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
           <t>18,17</t>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,21</t>
+          <t>19,25</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,71; 18,75</t>
+          <t>18,4; 20,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,66; 19,87</t>
+          <t>18,75; 20,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,72; 19,02</t>
+          <t>17,47; 18,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,43; 20,48</t>
+          <t>18,49; 20,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,35; 20,31</t>
+          <t>17,68; 18,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>18,65; 19,92</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>17,75; 19,01</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>18,41; 20,24</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>18,17; 19,28</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>18,87; 19,73</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>17,75; 18,66</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>18,69; 19,98</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17,51; 18,96</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>18,48; 20,43</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>18,22; 19,28</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>18,84; 19,71</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>17,77; 18,73</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>18,66; 20,05</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>20,48</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>21,6</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18,86</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>19,13</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>19,64</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>20,5</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>18,9</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18,32</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>20,48</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>21,6</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,86</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19,02</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,69</t>
+          <t>18,78</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,04; 20,41</t>
+          <t>19,75; 21,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,76; 21,34</t>
+          <t>20,46; 23,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,38; 19,88</t>
+          <t>18,31; 19,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,89; 18,75</t>
+          <t>18,65; 19,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,71; 21,53</t>
+          <t>19,04; 20,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,5; 23,9</t>
+          <t>19,69; 21,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,36; 19,56</t>
+          <t>18,36; 19,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,51; 19,55</t>
+          <t>17,95; 18,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,56; 20,64</t>
+          <t>19,54; 20,7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,42; 22,26</t>
+          <t>20,42; 22,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,37</t>
+          <t>18,49; 19,38</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,35; 19,04</t>
+          <t>18,46; 19,16</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>19,78</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19,94</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19,11</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19,41</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>19,01</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>19,29</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>18,82</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18,96</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>19,94</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,14</t>
+          <t>19,12</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,72; 19,28</t>
+          <t>19,45; 20,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,97; 19,64</t>
+          <t>19,56; 20,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,53; 19,14</t>
+          <t>18,8; 19,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18,56; 19,66</t>
+          <t>19,06; 19,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,46; 20,24</t>
+          <t>18,75; 19,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,55; 20,53</t>
+          <t>18,99; 19,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,75; 19,46</t>
+          <t>18,55; 19,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,94; 19,78</t>
+          <t>18,48; 19,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,66</t>
+          <t>19,18; 19,68</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,35; 19,94</t>
+          <t>19,37; 19,93</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,73; 19,21</t>
+          <t>18,73; 19,2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,87; 19,51</t>
+          <t>18,87; 19,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Provincia-trans_orig.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 79,86%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 87,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
